--- a/JsonConverter/ExcelFiles/Ability.xlsx
+++ b/JsonConverter/ExcelFiles/Ability.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">Ability 고유 ID</t>
   </si>
@@ -57,9 +57,6 @@
   <si>
     <t xml:space="preserve">EffectRound</t>
   </si>
-  <si>
-    <t xml:space="preserve">SaltDebuff</t>
-  </si>
 </sst>
 </file>
 
@@ -68,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -114,13 +111,6 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -189,39 +179,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -551,9 +541,7 @@
       <c r="J3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="8"/>
       <c r="B4" s="8" t="n">
         <v>10</v>
       </c>

--- a/JsonConverter/ExcelFiles/Ability.xlsx
+++ b/JsonConverter/ExcelFiles/Ability.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6EB691-0C3B-4FC6-A15F-8EE924E8ADEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E04AC3-1D30-4C02-80DB-41EE7EB6E8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Ability 고유 ID</t>
   </si>
@@ -101,6 +101,10 @@
   </si>
   <si>
     <t>Prefab/Ability/HealField</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrefabPath</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -553,7 +557,9 @@
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>

--- a/JsonConverter/ExcelFiles/Ability.xlsx
+++ b/JsonConverter/ExcelFiles/Ability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E04AC3-1D30-4C02-80DB-41EE7EB6E8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87369B9C-1284-40AE-B7FA-9992C7606C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>NumbericalValue</t>
   </si>
   <si>
-    <t>ActiveTime</t>
-  </si>
-  <si>
     <t>EffectRound</t>
   </si>
   <si>
@@ -105,6 +102,10 @@
   </si>
   <si>
     <t>PrefabPath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActiveTime</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -510,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -525,16 +526,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -552,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -567,7 +568,7 @@
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="9">
         <v>0</v>
@@ -582,7 +583,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -591,7 +592,7 @@
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="9">
         <v>10</v>
@@ -606,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -615,7 +616,7 @@
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="9">
         <v>0</v>
@@ -630,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -639,7 +640,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="9">
         <v>0</v>
@@ -654,7 +655,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
